--- a/Result/profitability/3218.xlsx
+++ b/Result/profitability/3218.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>2.71</v>
+        <v>2.68375</v>
       </c>
       <c r="N2" t="n">
-        <v>57.96625</v>
+        <v>57.87875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>2.30875</v>
+        <v>2.29</v>
       </c>
       <c r="N3" t="n">
-        <v>56.34500000000001</v>
+        <v>56.20875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.99</v>
+        <v>1.78875</v>
       </c>
       <c r="N4" t="n">
-        <v>54.21</v>
+        <v>54.00625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.32375</v>
+        <v>1.595</v>
       </c>
       <c r="N5" t="n">
-        <v>50.79125</v>
+        <v>50.62</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>1.26375</v>
+        <v>1.09125</v>
       </c>
       <c r="N6" t="n">
-        <v>49.90375</v>
+        <v>49.74625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>47.8325</v>
+        <v>47.70125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.215</v>
+        <v>0.135</v>
       </c>
       <c r="N8" t="n">
-        <v>47.055</v>
+        <v>47.0975</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-0.21375</v>
       </c>
       <c r="N9" t="n">
-        <v>45.58374999999999</v>
+        <v>45.58375</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3218</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1126</v>
+      </c>
+      <c r="D75" t="n">
+        <v>476</v>
+      </c>
+      <c r="E75" t="n">
+        <v>650</v>
+      </c>
+      <c r="F75" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="G75" t="n">
+        <v>348</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>30.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-53</v>
+      </c>
+      <c r="J75" t="n">
+        <v>295</v>
+      </c>
+      <c r="K75" t="n">
+        <v>226</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.9975</v>
+      </c>
+      <c r="N75" t="n">
+        <v>58.565</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.6400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1933534743202417</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3399999999999963</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.005925409550366023</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.370000000000005</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02318497207649362</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
